--- a/SYS/APDU_Electrical_Tables_R27.xlsx
+++ b/SYS/APDU_Electrical_Tables_R27.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rdc17f0df2b264429"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="2" r:id="R657251618d044136"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCBs" sheetId="3" r:id="Rb5058c891f2b490e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="4" r:id="R8a9857c67ef046cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cables" sheetId="5" r:id="Ra58aeda07a854a0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuses" sheetId="6" r:id="R838df2906f914d99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power" sheetId="7" r:id="R66260f9f14594b78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenItems" sheetId="8" r:id="Re88c5448730048b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="Rb89b5c92816c4f34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf3ca079fa1bf4020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="2" r:id="R345d9ac0df1f4cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCBs" sheetId="3" r:id="R6fdd4ad302c64308"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="4" r:id="Rca6d5e3647124de2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cables" sheetId="5" r:id="R8e989bb7f8fc4332"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuses" sheetId="6" r:id="Race40e9a8ab9481b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power" sheetId="7" r:id="Rd958b683bb5e4a31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenItems" sheetId="8" r:id="Raf2c63e3e76345df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="Rffc7b5049a82443f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,7 +27,7 @@
     <x:numFmt numFmtId="202" formatCode="0.000"/>
     <x:numFmt numFmtId="203" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -63,6 +63,10 @@
       <x:sz val="11"/>
       <x:color rgb="FF175B98"/>
       <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
   <x:fills count="5">
@@ -108,7 +112,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -190,6 +194,13 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -444,10 +455,10 @@
         <x:v>Power</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>One RSP-500-24 (24 V / 21 A / 504 W). SYSCTRL generates 12 V. IOCTRL module = 24 V; relay COM = derived 12 V.</x:v>
+        <x:v>One RSP-500-24 (24 V / 21 A / 504 W) feeds SYSCTRL. One onboard SMPS generates 12 V; power connectors belong to SYSCTRL.</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>No independent 12 V or 48 V PSU. Gantry 24 V compatibility and full power capacity are not established.</x:v>
+        <x:v>No separate distribution assembly or 12 V/48 V PSU. Branch implementation, SMPS selection and complete capacity remain pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="44" customHeight="1">
@@ -499,10 +510,10 @@
         <x:v>Harnesses</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>Cables retain W01–W39 IDs; inactive IDs have quantity 0. H/J formulas give known lengths and stock only.</x:v>
+        <x:v>W01-W39 retained. W04/W06/W07 are internalized and have zero external-harness quantity; W14/W22 retired. 28 required external cable types.</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>Blank route lengths remain pending. Cable/connector gauge, colour, shielding and pinout are not manufacturing-approved.</x:v>
+        <x:v>Five route lengths remain unknown. 109.5 m is only the known external routing subtotal; W03 route must be remeasured for the SYSCTRL input.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
@@ -510,10 +521,10 @@
         <x:v>Scope exclusions</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>No UPS, battery or cellular. Optional Wi-Fi/BLE, camera/OCR, lighting, NFC and door actuators have quantity 0.</x:v>
+        <x:v>No UPS, battery or cellular. Wi-Fi/BLE, camera/OCR, interior lighting and door actuators remain excluded. NFC antenna selected: Molex 1462362151.</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>Label marker remains required but unspecified; its control and supply interfaces are held.</x:v>
+        <x:v>NFC reader/front-end and marker remain unselected. Both require interface and power budgeting; no payment terminal is approved.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
@@ -543,10 +554,10 @@
         <x:v>Release gates</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>OpenItems lists unresolved supplier, design, integration and customer decisions.</x:v>
+        <x:v>Corrected against merged SYSCTRL diagram and NFC antenna selection. F1-F18 are branch references; protection implementation TBC. OpenItems O01-O16.</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>This review aligns documents; it does not certify fabrication readiness.</x:v>
+        <x:v>No 17-DIN-holder purchase assumption. Component register synchronized. Presentation remains an earlier review snapshot; use this workbook for current electrical schedules.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -704,7 +715,7 @@
         <x:v>SELECTED / engineering pending</x:v>
       </x:c>
       <x:c r="G7" s="9" t="str">
-        <x:v>Buck and drivers pending; local servo rail voltage TBC.</x:v>
+        <x:v>Single 24 V system input; integrated power routing/connectors and one 12 V SMPS. Protection and local servo rail pending.</x:v>
       </x:c>
       <x:c r="H7" s="9" t="str">
         <x:v>S01/S03/S04</x:v>
@@ -819,22 +830,22 @@
         <x:v>DIST24</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>24 V main distribution and terminals</x:v>
+        <x:v>SYSCTRL 24 V distribution function</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>TBC</x:v>
+        <x:v>Internal PCB routing / connectors; MPN TBC</x:v>
       </x:c>
       <x:c r="D12" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E12" s="10" t="str">
-        <x:v>BUY</x:v>
+        <x:v>IN SYSCTRL</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
-        <x:v>HOLD</x:v>
+        <x:v>INTERNAL / HOLD</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>Must carry total PSU output; not one 6.3 A fuse holder.</x:v>
+        <x:v>Functional allocation within SYSCTRL; not an independent distribution assembly. Do not buy as a separate module.</x:v>
       </x:c>
       <x:c r="H12" s="10" t="str">
         <x:v>O06</x:v>
@@ -845,22 +856,22 @@
         <x:v>DIST12</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>Separate derived 12 V distribution</x:v>
+        <x:v>SYSCTRL derived 12 V distribution function</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>TBC</x:v>
+        <x:v>Internal PCB routing / connectors; MPN TBC</x:v>
       </x:c>
       <x:c r="D13" s="9" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
-        <x:v>BUY</x:v>
+        <x:v>IN SYSCTRL</x:v>
       </x:c>
       <x:c r="F13" s="9" t="str">
-        <x:v>HOLD</x:v>
+        <x:v>INTERNAL / HOLD</x:v>
       </x:c>
       <x:c r="G13" s="9" t="str">
-        <x:v>Fed from SYSCTRL J43/W04.</x:v>
+        <x:v>Functional allocation within SYSCTRL; not an independent distribution assembly. Do not buy as a separate module.</x:v>
       </x:c>
       <x:c r="H13" s="9" t="str">
         <x:v>O02/O06</x:v>
@@ -871,22 +882,22 @@
         <x:v>DIN-F</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>DIN fuse positions</x:v>
+        <x:v>Previous DIN fuse-holder assumption</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>Phoenix 3046032 candidate</x:v>
+        <x:v>No released holder selection</x:v>
       </x:c>
       <x:c r="D14" s="10" t="n">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E14" s="10" t="str">
-        <x:v>BUY</x:v>
+        <x:v>RETIRED</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
-        <x:v>CANDIDATE</x:v>
+        <x:v>WITHDRAWN</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
-        <x:v>F1–F13 and F15–F18; F12 holder/current must be reselected if necessary.</x:v>
+        <x:v>The previous 17 x Phoenix 3046032 assumption is withdrawn. Final branch-protection implementation and physical quantities TBC.</x:v>
       </x:c>
       <x:c r="H14" s="10" t="str">
         <x:v>S11/O06</x:v>
@@ -897,22 +908,22 @@
         <x:v>F1–F18</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>Fuse elements</x:v>
+        <x:v>Branch-protection references</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>TBC by branch schedule</x:v>
+        <x:v>TBC by branch design</x:v>
       </x:c>
       <x:c r="D15" s="9" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>BUY</x:v>
+        <x:v>FUNCTIONAL COUNT</x:v>
       </x:c>
       <x:c r="F15" s="9" t="str">
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="G15" s="9" t="str">
-        <x:v>17 DIN + F14 on SYSCTRL; element curves/DC interruption/ratings not released.</x:v>
+        <x:v>18 protected branch references, not 18 finalized fuse elements. Select technology, placement, ratings and actual purchase counts during SYSCTRL design.</x:v>
       </x:c>
       <x:c r="H15" s="9" t="str">
         <x:v>Fuses/O06</x:v>
@@ -923,7 +934,7 @@
         <x:v>BUCK12</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>On-board 24→12 V converter</x:v>
+        <x:v>Onboard 24 V-to-12 V SMPS</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
         <x:v>TBC</x:v>
@@ -938,7 +949,7 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
-        <x:v>Not a separate module; include in SYSCTRL component BOM when designed.</x:v>
+        <x:v>One conversion stage inside SYSCTRL. Input/output rails are internal; no external converter or distribution module.</x:v>
       </x:c>
       <x:c r="H16" s="10" t="str">
         <x:v>O02</x:v>
@@ -1625,25 +1636,25 @@
         <x:v>NFC</x:v>
       </x:c>
       <x:c r="B43" s="9" t="str">
-        <x:v>NFC/payment reader</x:v>
+        <x:v>NFC reader / front-end function</x:v>
       </x:c>
       <x:c r="C43" s="9" t="str">
         <x:v>TBC</x:v>
       </x:c>
       <x:c r="D43" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E43" s="9" t="str">
-        <x:v>OPTION</x:v>
+        <x:v>FUNCTIONAL ALLOWANCE</x:v>
       </x:c>
       <x:c r="F43" s="9" t="str">
-        <x:v>EXCLUDED</x:v>
+        <x:v>HOLD O16</x:v>
       </x:c>
       <x:c r="G43" s="9" t="str">
-        <x:v>Not approved; excluded from committed quantities and power subtotal.</x:v>
+        <x:v>One reader function planned for selected antenna; IC/module, board allocation, host interface, supply and implementation quantity pending. Not a selected payment terminal.</x:v>
       </x:c>
       <x:c r="H43" s="9" t="str">
-        <x:v>O13</x:v>
+        <x:v>O16</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="44" customHeight="1">
@@ -1774,6 +1785,32 @@
       </x:c>
       <x:c r="H48" s="10" t="str">
         <x:v>S01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="75" customHeight="1">
+      <x:c r="A49" s="32" t="str">
+        <x:v>ANT-NFC</x:v>
+      </x:c>
+      <x:c r="B49" s="32" t="str">
+        <x:v>NFC antenna</x:v>
+      </x:c>
+      <x:c r="C49" s="32" t="str">
+        <x:v>Molex 1462362151</x:v>
+      </x:c>
+      <x:c r="D49" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E49" s="32" t="str">
+        <x:v>BUY</x:v>
+      </x:c>
+      <x:c r="F49" s="32" t="str">
+        <x:v>SELECTED / integration pending</x:v>
+      </x:c>
+      <x:c r="G49" s="32" t="str">
+        <x:v>13.56 MHz; 15 x 15 x 0.27 mm; adhesive; 102 mm cable; 2.40 uH. One per machine planning quantity. Reader matching, termination and mounting TBC.</x:v>
+      </x:c>
+      <x:c r="H49" s="32" t="str">
+        <x:v>S14/S15/O16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1899,16 +1936,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E6" s="10" t="str">
-        <x:v>24 V via F11/W06 and F12/W07</x:v>
+        <x:v>24 V directly from PSU1 via W03; input connector MPN TBC</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
-        <x:v>Gantry/labeling; on-board 24→12 V; F14 lane logic</x:v>
+        <x:v>Gantry/labeling, internal power routing and connectors, one onboard 24 V-to-12 V SMPS</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
         <x:v>FW_ADHERENT_SYSCTRL_R1</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
-        <x:v>Buck and drivers pending; local servo rail voltage TBC.</x:v>
+        <x:v>SMPS, branch protection and connector pinouts pending. W04/W06/W07 are no longer external harnesses.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="44" customHeight="1">
@@ -2002,7 +2039,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>System-side mating sets are candidates until exact components, gauge, geometry and derating are approved. COTS boards retain their native connectors.</x:v>
+        <x:v>Quantities count interface circuits/positions, not finalized connector housings. SYSCTRL contains the power connection area; no separate distribution unit.</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -2142,31 +2179,29 @@
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="10" t="str">
-        <x:v>F1–F13, F15–F18</x:v>
+        <x:v>F1–F18</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>24 V + derived 12 V branch protection</x:v>
+        <x:v>Branch-protection references</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>DIN rail; F14 is on SYSCTRL</x:v>
+        <x:v>SYSCTRL branches; final location TBC</x:v>
       </x:c>
       <x:c r="D8" s="10" t="str">
-        <x:v>5x20 holder candidate; F12 selection pending</x:v>
+        <x:v>Protection technology / package TBC</x:v>
       </x:c>
       <x:c r="E8" s="10" t="str">
-        <x:v>Phoenix 3046032 (6.3 A nominal)</x:v>
+        <x:v>TBC</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
-        <x:v>Fuse element MPN/rating TBC</x:v>
-      </x:c>
-      <x:c r="G8" s="10" t="n">
-        <x:v>17</x:v>
-      </x:c>
+        <x:v>Not a connector schedule item</x:v>
+      </x:c>
+      <x:c r="G8" s="10"/>
       <x:c r="H8" s="10" t="str">
-        <x:v>CANDIDATE / HOLD O06</x:v>
+        <x:v>HOLD O06</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>17 DIN positions; do not use 6.3 A holder if revised F12 requires more current.</x:v>
+        <x:v>18 logical branch references in Fuses sheet; no committed DIN-holder count.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
@@ -2464,28 +2499,28 @@
         <x:v>J29</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>24 V motor supply in (F11)</x:v>
+        <x:v>Former external motor-rail input W06</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>SYSCTRL</x:v>
+        <x:v>SYSCTRL internal function</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>Power connector; pin count/gauge/current TBC</x:v>
+        <x:v>No external connector assigned</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>TBC</x:v>
+        <x:v>Not fitted for former loop</x:v>
       </x:c>
       <x:c r="F19" s="9" t="str">
-        <x:v>TBC</x:v>
+        <x:v>Not fitted</x:v>
       </x:c>
       <x:c r="G19" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H19" s="9" t="str">
-        <x:v>CANDIDATE</x:v>
+        <x:v>RETIRED ALLOCATION</x:v>
       </x:c>
       <x:c r="I19" s="9" t="str">
-        <x:v>Final mating set, keying, gauge and derating require approval.</x:v>
+        <x:v>Legacy reference retained; no extra external cable/mate. Final SYSCTRL connector references below remain TBC.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="44" customHeight="1">
@@ -2551,28 +2586,28 @@
         <x:v>J41</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>24 V input from F12 to on-board buck</x:v>
+        <x:v>Former external SMPS input W07</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>SYSCTRL</x:v>
+        <x:v>SYSCTRL internal function</x:v>
       </x:c>
       <x:c r="D22" s="10" t="str">
-        <x:v>Power connector; input current TBC</x:v>
+        <x:v>No external connector assigned</x:v>
       </x:c>
       <x:c r="E22" s="10" t="str">
-        <x:v>TBC</x:v>
+        <x:v>Not fitted for former loop</x:v>
       </x:c>
       <x:c r="F22" s="10" t="str">
-        <x:v>TBC</x:v>
+        <x:v>Not fitted</x:v>
       </x:c>
       <x:c r="G22" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="10" t="str">
-        <x:v>CANDIDATE</x:v>
+        <x:v>RETIRED ALLOCATION</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
-        <x:v>Final mating set, keying, gauge and derating require approval.</x:v>
+        <x:v>Legacy reference retained; no extra external cable/mate. Final SYSCTRL connector references below remain TBC.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="44" customHeight="1">
@@ -2696,28 +2731,28 @@
         <x:v>J43</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>12 V buck output to distribution</x:v>
+        <x:v>Former external SMPS output loop W04</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v>SYSCTRL</x:v>
+        <x:v>SYSCTRL internal function</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>Power connector; output current TBC</x:v>
+        <x:v>No external connector assigned</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>TBC</x:v>
+        <x:v>Not fitted for former loop</x:v>
       </x:c>
       <x:c r="F27" s="9" t="str">
-        <x:v>TBC</x:v>
+        <x:v>Not fitted</x:v>
       </x:c>
       <x:c r="G27" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="9" t="str">
-        <x:v>HOLD O02</x:v>
+        <x:v>RETIRED ALLOCATION</x:v>
       </x:c>
       <x:c r="I27" s="9" t="str">
-        <x:v>W04; not an external 12 V input.</x:v>
+        <x:v>Legacy reference retained; no extra external cable/mate. Final SYSCTRL connector references below remain TBC.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="44" customHeight="1">
@@ -2774,6 +2809,209 @@
       </x:c>
       <x:c r="I29" s="9" t="str">
         <x:v>W37 bonding assembly; counts await enclosure bonding plan.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="85" customHeight="1">
+      <x:c r="A30" s="3" t="str">
+        <x:v>SYSCTRL-PWR-IN (TBC)</x:v>
+      </x:c>
+      <x:c r="B30" s="3" t="str">
+        <x:v>24 V system power input</x:v>
+      </x:c>
+      <x:c r="C30" s="3" t="str">
+        <x:v>SYSCTRL</x:v>
+      </x:c>
+      <x:c r="D30" s="3" t="str">
+        <x:v>Power connector rated for total machine input; TBC</x:v>
+      </x:c>
+      <x:c r="E30" s="3" t="str">
+        <x:v>TBC</x:v>
+      </x:c>
+      <x:c r="F30" s="3" t="str">
+        <x:v>PSU1 screw terminals to selected SYSCTRL mate</x:v>
+      </x:c>
+      <x:c r="G30" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H30" s="3" t="str">
+        <x:v>HOLD O06</x:v>
+      </x:c>
+      <x:c r="I30" s="3" t="str">
+        <x:v>W03. Rating, gauge, inrush and PCB current paths must cover all simultaneous loads.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="85" customHeight="1">
+      <x:c r="A31" s="3" t="str">
+        <x:v>SYSCTRL-24V-LANE (TBC)</x:v>
+      </x:c>
+      <x:c r="B31" s="3" t="str">
+        <x:v>24 V row power outputs</x:v>
+      </x:c>
+      <x:c r="C31" s="3" t="str">
+        <x:v>SYSCTRL</x:v>
+      </x:c>
+      <x:c r="D31" s="3" t="str">
+        <x:v>F1-F10 branch outputs; connector MPN/pins TBC</x:v>
+      </x:c>
+      <x:c r="E31" s="3" t="str">
+        <x:v>TBC</x:v>
+      </x:c>
+      <x:c r="F31" s="3" t="str">
+        <x:v>LANECTRL J5 candidate</x:v>
+      </x:c>
+      <x:c r="G31" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H31" s="3" t="str">
+        <x:v>HOLD O06</x:v>
+      </x:c>
+      <x:c r="I31" s="3" t="str">
+        <x:v>W24, ten branch circuits. Physical housings may combine circuits; packaging TBC.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="85" customHeight="1">
+      <x:c r="A32" s="3" t="str">
+        <x:v>SYSCTRL-24V-DRIVE (TBC)</x:v>
+      </x:c>
+      <x:c r="B32" s="3" t="str">
+        <x:v>Proposed 24 V X/Z drive outputs</x:v>
+      </x:c>
+      <x:c r="C32" s="3" t="str">
+        <x:v>SYSCTRL</x:v>
+      </x:c>
+      <x:c r="D32" s="3" t="str">
+        <x:v>F15/F16 branch outputs; connector MPN/pins TBC</x:v>
+      </x:c>
+      <x:c r="E32" s="3" t="str">
+        <x:v>TBC</x:v>
+      </x:c>
+      <x:c r="F32" s="3" t="str">
+        <x:v>Native drive mates TBC</x:v>
+      </x:c>
+      <x:c r="G32" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H32" s="3" t="str">
+        <x:v>HOLD O01/O06</x:v>
+      </x:c>
+      <x:c r="I32" s="3" t="str">
+        <x:v>W29/W30. 24 V compatibility and current need supplier evidence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="85" customHeight="1">
+      <x:c r="A33" s="3" t="str">
+        <x:v>SYSCTRL-24V-IO (TBC)</x:v>
+      </x:c>
+      <x:c r="B33" s="3" t="str">
+        <x:v>24 V IOCTRL module output</x:v>
+      </x:c>
+      <x:c r="C33" s="3" t="str">
+        <x:v>SYSCTRL</x:v>
+      </x:c>
+      <x:c r="D33" s="3" t="str">
+        <x:v>F17 branch output; connector MPN/pins TBC</x:v>
+      </x:c>
+      <x:c r="E33" s="3" t="str">
+        <x:v>TBC</x:v>
+      </x:c>
+      <x:c r="F33" s="3" t="str">
+        <x:v>IOCTRL native power terminals</x:v>
+      </x:c>
+      <x:c r="G33" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H33" s="3" t="str">
+        <x:v>HOLD O06</x:v>
+      </x:c>
+      <x:c r="I33" s="3" t="str">
+        <x:v>W34. Separate from 12 V relay-contact feed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="85" customHeight="1">
+      <x:c r="A34" s="3" t="str">
+        <x:v>SYSCTRL-12V-MAIN (TBC)</x:v>
+      </x:c>
+      <x:c r="B34" s="3" t="str">
+        <x:v>Derived 12 V MAINCTRL output</x:v>
+      </x:c>
+      <x:c r="C34" s="3" t="str">
+        <x:v>SYSCTRL</x:v>
+      </x:c>
+      <x:c r="D34" s="3" t="str">
+        <x:v>F13 branch output; connector MPN/pins TBC</x:v>
+      </x:c>
+      <x:c r="E34" s="3" t="str">
+        <x:v>TBC</x:v>
+      </x:c>
+      <x:c r="F34" s="3" t="str">
+        <x:v>MYIR J46 native power plug TBC</x:v>
+      </x:c>
+      <x:c r="G34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H34" s="3" t="str">
+        <x:v>HOLD O02/O06</x:v>
+      </x:c>
+      <x:c r="I34" s="3" t="str">
+        <x:v>W05. Generated by the single onboard SMPS.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="85" customHeight="1">
+      <x:c r="A35" s="3" t="str">
+        <x:v>SYSCTRL-12V-LATCH (TBC)</x:v>
+      </x:c>
+      <x:c r="B35" s="3" t="str">
+        <x:v>Derived 12 V latch-contact output</x:v>
+      </x:c>
+      <x:c r="C35" s="3" t="str">
+        <x:v>SYSCTRL</x:v>
+      </x:c>
+      <x:c r="D35" s="3" t="str">
+        <x:v>F18 branch output; connector MPN/pins TBC</x:v>
+      </x:c>
+      <x:c r="E35" s="3" t="str">
+        <x:v>TBC</x:v>
+      </x:c>
+      <x:c r="F35" s="3" t="str">
+        <x:v>IOCTRL relay COM terminals</x:v>
+      </x:c>
+      <x:c r="G35" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H35" s="3" t="str">
+        <x:v>HOLD O02/O06</x:v>
+      </x:c>
+      <x:c r="I35" s="3" t="str">
+        <x:v>W35. Lane-logic 12 V is already allocated to J15A; do not duplicate it.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="85" customHeight="1">
+      <x:c r="A36" s="32" t="str">
+        <x:v>NFC-RF (TBC)</x:v>
+      </x:c>
+      <x:c r="B36" s="32" t="str">
+        <x:v>NFC antenna to reader front end</x:v>
+      </x:c>
+      <x:c r="C36" s="32" t="str">
+        <x:v>Antenna / reader location TBC</x:v>
+      </x:c>
+      <x:c r="D36" s="32" t="str">
+        <x:v>RF termination and matching TBC</x:v>
+      </x:c>
+      <x:c r="E36" s="32" t="str">
+        <x:v>Molex 1462362151 antenna</x:v>
+      </x:c>
+      <x:c r="F36" s="32" t="str">
+        <x:v>Reader-side connection TBC</x:v>
+      </x:c>
+      <x:c r="G36" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H36" s="32" t="str">
+        <x:v>HOLD O16</x:v>
+      </x:c>
+      <x:c r="I36" s="32" t="str">
+        <x:v>102 mm antenna cable is included in the selected antenna; not a separately selected coax jumper. Verify actual termination from drawing.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2821,7 +3059,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>Direct sensor runs; no junction boxes. Route quantities are grouped by W identifier; missing lengths are unresolved, not zero-length requirements.</x:v>
+        <x:v>28 required external cable types. W04/W06/W07 are internalized, not external jumpers. W14/W22 remain retired; sensors connect directly to controller boards.</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -2972,16 +3210,16 @@
         <x:v>W03</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>WR_ADHERENT_PSU24_TO_DIST_R1</x:v>
+        <x:v>WR_ADHERENT_PSU24_TO_SYSCTRL_R1</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>PSU1 → DIN fuse block</x:v>
+        <x:v>PSU1 24 V output → SYSCTRL system power input</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
         <x:v>Power pair; gauge/current rating TBC; no assumed parallel-pin capacity</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>ferrule both ends</x:v>
+        <x:v>PSU screw terminals → SYSCTRL power mate TBC</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
         <x:v>1</x:v>
@@ -3004,7 +3242,7 @@
         <x:v>REQUIRED / provisional</x:v>
       </x:c>
       <x:c r="L7" s="9" t="str">
-        <x:v>Length estimate; pinout, gauge and current rating not released.</x:v>
+        <x:v>0.5 m retained only as a route allowance, not a measured cut length. Size for combined machine input, SMPS inrush and PCB/connector limits.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
@@ -3012,26 +3250,26 @@
         <x:v>W04</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>WR_ADHERENT_SYSCTRL_TO_DIST_12V_R1</x:v>
+        <x:v>INTERNALIZED_W04</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>SYSCTRL J43 → separate 12 V distribution rail</x:v>
+        <x:v>12 V SMPS output to internal SYSCTRL rail</x:v>
       </x:c>
       <x:c r="D8" s="10" t="str">
-        <x:v>Power pair; gauge/rating TBC</x:v>
+        <x:v>PCB routing; not an external cable</x:v>
       </x:c>
       <x:c r="E8" s="10" t="str">
-        <x:v>SYSCTRL power connector TBC → ferrules</x:v>
+        <x:v>No external mating set</x:v>
       </x:c>
       <x:c r="F8" s="12" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G8" s="15" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="16" t="n">
         <x:f>IF(ISNUMBER(G8),F8*G8,0)</x:f>
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="16" t="n">
         <x:v>0</x:v>
@@ -3041,10 +3279,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>REQUIRED / provisional</x:v>
+        <x:v>INTERNALIZED / zero harness</x:v>
       </x:c>
       <x:c r="L8" s="10" t="str">
-        <x:v>Length estimate; pinout, gauge and current rating not released.</x:v>
+        <x:v>Legacy W ID retained only for traceability. Removed external loop between SYSCTRL and the former distribution box.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
@@ -3052,16 +3290,16 @@
         <x:v>W05</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>WR_ADHERENT_DIST_TO_MAINCTRL_R1</x:v>
+        <x:v>WR_ADHERENT_SYSCTRL_TO_MAINCTRL_R1</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>F13 → MAINCTRL J46</x:v>
+        <x:v>SYSCTRL F13 / 12 V output → MAINCTRL J46</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
         <x:v>12 V power pair; gauge and MYIR plug TBC</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
-        <x:v>ferrule → MYIR 12 V power plug (board DC input)</x:v>
+        <x:v>SYSCTRL mating power connector TBC → native / selected load connector</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
         <x:v>1</x:v>
@@ -3092,26 +3330,26 @@
         <x:v>W06</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>WR_ADHERENT_DIST_TO_SYSCTRL_24V_R1</x:v>
+        <x:v>INTERNALIZED_W06</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>F11 → SYSCTRL J29 (chuck steppers)</x:v>
+        <x:v>24 V SYSCTRL internal motor branch</x:v>
       </x:c>
       <x:c r="D10" s="10" t="str">
-        <x:v>Power pair; gauge/current rating TBC; no assumed parallel-pin capacity</x:v>
+        <x:v>PCB routing; not an external cable</x:v>
       </x:c>
       <x:c r="E10" s="10" t="str">
-        <x:v>ferrules → candidate power connector; mating set / pin allocation TBC</x:v>
+        <x:v>No external mating set</x:v>
       </x:c>
       <x:c r="F10" s="12" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G10" s="15" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="16" t="n">
         <x:f>IF(ISNUMBER(G10),F10*G10,0)</x:f>
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="16" t="n">
         <x:v>0</x:v>
@@ -3121,10 +3359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>REQUIRED / provisional</x:v>
+        <x:v>INTERNALIZED / zero harness</x:v>
       </x:c>
       <x:c r="L10" s="10" t="str">
-        <x:v>Length estimate; pinout, gauge and current rating not released.</x:v>
+        <x:v>Legacy W ID retained only for traceability. Removed external loop between SYSCTRL and the former distribution box.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
@@ -3132,26 +3370,26 @@
         <x:v>W07</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>WR_ADHERENT_DIST_TO_SYSCTRL_BUCK24V_R1</x:v>
+        <x:v>INTERNALIZED_W07</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>F12 (24 V) → SYSCTRL J41 buck input</x:v>
+        <x:v>24 V internal SMPS input branch</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>Power pair; gauge/rating TBC</x:v>
+        <x:v>PCB routing; not an external cable</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>ferrules → power connector TBC</x:v>
+        <x:v>No external mating set</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G11" s="13" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="14" t="n">
         <x:f>IF(ISNUMBER(G11),F11*G11,0)</x:f>
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
         <x:v>0</x:v>
@@ -3161,10 +3399,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K11" s="9" t="str">
-        <x:v>REQUIRED / provisional</x:v>
+        <x:v>INTERNALIZED / zero harness</x:v>
       </x:c>
       <x:c r="L11" s="9" t="str">
-        <x:v>Length estimate; pinout, gauge and current rating not released.</x:v>
+        <x:v>Legacy W ID retained only for traceability. Removed external loop between SYSCTRL and the former distribution box.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
@@ -3808,16 +4046,16 @@
         <x:v>W24</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>WR_ADHERENT_DIST_TO_LANECTRLnn_R1</x:v>
+        <x:v>WR_ADHERENT_SYSCTRL_TO_LANECTRLnn_R1</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>F1–F10 → LANECTRL-01…10 J5</x:v>
+        <x:v>SYSCTRL F1-F10 / 24 V row outputs → LANECTRL-01…10 J5</x:v>
       </x:c>
       <x:c r="D28" s="10" t="str">
         <x:v>Power pair; gauge/current rating TBC; no assumed parallel-pin capacity</x:v>
       </x:c>
       <x:c r="E28" s="10" t="str">
-        <x:v>ferrules → candidate power connector; mating set / pin allocation TBC</x:v>
+        <x:v>SYSCTRL mating power connector TBC → native / selected load connector</x:v>
       </x:c>
       <x:c r="F28" s="12" t="n">
         <x:v>10</x:v>
@@ -4008,16 +4246,16 @@
         <x:v>W29</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>WR_ADHERENT_DIST_TO_XDRIVE_24V_R1</x:v>
+        <x:v>WR_ADHERENT_SYSCTRL_TO_XDRIVE_24V_R1</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
-        <x:v>F15 → X drive unit power</x:v>
+        <x:v>SYSCTRL F15 / proposed 24 V output → X drive</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
         <x:v>Flexible power pair; gauge TBC; 24 V compatibility unverified</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
-        <x:v>ferrule → drive terminal (TBC)</x:v>
+        <x:v>SYSCTRL mating power connector TBC → native / selected load connector</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:v>1</x:v>
@@ -4048,16 +4286,16 @@
         <x:v>W30</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>WR_ADHERENT_DIST_TO_ZDRIVE_24V_R1</x:v>
+        <x:v>WR_ADHERENT_SYSCTRL_TO_ZDRIVE_24V_R1</x:v>
       </x:c>
       <x:c r="C34" s="10" t="str">
-        <x:v>F16 → Z drive unit power (via X chain)</x:v>
+        <x:v>SYSCTRL F16 / proposed 24 V output → Z drive</x:v>
       </x:c>
       <x:c r="D34" s="10" t="str">
         <x:v>Flexible power pair; gauge TBC; 24 V compatibility unverified</x:v>
       </x:c>
       <x:c r="E34" s="10" t="str">
-        <x:v>ferrule → drive terminal (TBC)</x:v>
+        <x:v>SYSCTRL mating power connector TBC → native / selected load connector</x:v>
       </x:c>
       <x:c r="F34" s="12" t="n">
         <x:v>1</x:v>
@@ -4208,16 +4446,16 @@
         <x:v>W34</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>WR_ADHERENT_DIST_TO_IOCTRL_R1</x:v>
+        <x:v>WR_ADHERENT_SYSCTRL_TO_IOCTRL_R1</x:v>
       </x:c>
       <x:c r="C38" s="10" t="str">
-        <x:v>F17 (24 V) → IOCTRL module power terminals</x:v>
+        <x:v>SYSCTRL F17 / 24 V output → IOCTRL module power</x:v>
       </x:c>
       <x:c r="D38" s="10" t="str">
         <x:v>24 V power pair; gauge TBC</x:v>
       </x:c>
       <x:c r="E38" s="10" t="str">
-        <x:v>ferrules at both ends</x:v>
+        <x:v>SYSCTRL mating power connector TBC → native / selected load connector</x:v>
       </x:c>
       <x:c r="F38" s="12" t="n">
         <x:v>1</x:v>
@@ -4248,16 +4486,16 @@
         <x:v>W35</x:v>
       </x:c>
       <x:c r="B39" s="9" t="str">
-        <x:v>WR_ADHERENT_DIST12_TO_IOCTRL_COM_R1</x:v>
+        <x:v>WR_ADHERENT_SYSCTRL12_TO_IOCTRL_COM_R1</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
-        <x:v>F18 (derived 12 V) → IOCTRL relay COM and latch returns</x:v>
+        <x:v>SYSCTRL F18 / derived 12 V output → IOCTRL relay COM and latch returns</x:v>
       </x:c>
       <x:c r="D39" s="9" t="str">
         <x:v>Power pair; gauge TBC</x:v>
       </x:c>
       <x:c r="E39" s="9" t="str">
-        <x:v>ferrules</x:v>
+        <x:v>SYSCTRL mating power connector TBC → native / selected load connector</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
         <x:v>1</x:v>
@@ -4447,12 +4685,12 @@
       </x:c>
       <x:c r="F45" t="n">
         <x:f>SUM(F5:F43)</x:f>
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G45" s="17"/>
       <x:c r="H45" s="17" t="n">
         <x:f>SUM(H5:H43)</x:f>
-        <x:v>111</x:v>
+        <x:v>109.5</x:v>
       </x:c>
       <x:c r="I45" s="17"/>
       <x:c r="J45" s="17" t="n">
@@ -4529,7 +4767,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>F14 is on SYSCTRL. There are 17 DIN positions plus 1 PCB branch protection position. Listed ratings are candidates, not released selections.</x:v>
+        <x:v>18 functional branch references retained. Protection technology, placement and actual fuse/holder purchase quantities remain TBC; no separate 17-position DIN block.</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -4566,7 +4804,7 @@
         <x:v>Location</x:v>
       </x:c>
       <x:c r="F4" s="8" t="str">
-        <x:v>Positions</x:v>
+        <x:v>Branch references</x:v>
       </x:c>
       <x:c r="G4" s="8" t="str">
         <x:v>Cable</x:v>
@@ -4589,7 +4827,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>DIN</x:v>
+        <x:v>SYSCTRL branch; placement TBC</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
         <x:v>10</x:v>
@@ -4615,13 +4853,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E6" s="10" t="str">
-        <x:v>DIN</x:v>
+        <x:v>SYSCTRL branch; placement TBC</x:v>
       </x:c>
       <x:c r="F6" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
-        <x:v>W06</x:v>
+        <x:v>Internal branch</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
         <x:v>Candidate; actual motor input and brake currents TBC.</x:v>
@@ -4639,16 +4877,16 @@
       </x:c>
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9" t="str">
-        <x:v>DIN</x:v>
+        <x:v>SYSCTRL branch; placement TBC</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="9" t="str">
-        <x:v>W07</x:v>
+        <x:v>Internal SMPS branch</x:v>
       </x:c>
       <x:c r="H7" s="9" t="str">
-        <x:v>Resize using converter input, inrush and efficiency; holder may need &gt;6.3 A.</x:v>
+        <x:v>Size for selected SMPS input, efficiency and inrush. Select protection/holder technology after current is known; no 6.3 A holder assumption.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
@@ -4665,7 +4903,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E8" s="10" t="str">
-        <x:v>DIN</x:v>
+        <x:v>SYSCTRL branch; placement TBC</x:v>
       </x:c>
       <x:c r="F8" s="10" t="n">
         <x:v>1</x:v>
@@ -4715,7 +4953,7 @@
       </x:c>
       <x:c r="D10" s="10"/>
       <x:c r="E10" s="10" t="str">
-        <x:v>DIN</x:v>
+        <x:v>SYSCTRL branch; placement TBC</x:v>
       </x:c>
       <x:c r="F10" s="10" t="n">
         <x:v>1</x:v>
@@ -4739,7 +4977,7 @@
       </x:c>
       <x:c r="D11" s="9"/>
       <x:c r="E11" s="9" t="str">
-        <x:v>DIN</x:v>
+        <x:v>SYSCTRL branch; placement TBC</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
         <x:v>1</x:v>
@@ -4763,7 +5001,7 @@
       </x:c>
       <x:c r="D12" s="10"/>
       <x:c r="E12" s="10" t="str">
-        <x:v>DIN</x:v>
+        <x:v>SYSCTRL branch; placement TBC</x:v>
       </x:c>
       <x:c r="F12" s="10" t="n">
         <x:v>1</x:v>
@@ -4787,7 +5025,7 @@
       </x:c>
       <x:c r="D13" s="9"/>
       <x:c r="E13" s="9" t="str">
-        <x:v>DIN</x:v>
+        <x:v>SYSCTRL branch; placement TBC</x:v>
       </x:c>
       <x:c r="F13" s="9" t="n">
         <x:v>1</x:v>
@@ -4844,7 +5082,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>24 V direct loads plus the input power of the SYSCTRL 12 V converter. All calculated currents are planning values; unknown loads block a capacity approval.</x:v>
+        <x:v>One 24 V system input to SYSCTRL. Known direct loads plus one onboard 12 V SMPS input; internal wiring changes do not remove electrical loads. Unknown loads block approval.</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -5595,6 +5833,43 @@
         <x:v>Excluded until approved; no current budget committed.</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" ht="75" customHeight="1">
+      <x:c r="A22" s="32" t="str">
+        <x:v>TBC</x:v>
+      </x:c>
+      <x:c r="B22" s="32" t="str">
+        <x:v>Unassigned</x:v>
+      </x:c>
+      <x:c r="C22" s="32" t="str">
+        <x:v>NFC reader / front end</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F22" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" s="32"/>
+      <x:c r="H22" s="32"/>
+      <x:c r="I22" s="32" t="n">
+        <x:f>IF(ISNUMBER(G22),E22*G22,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J22" s="32" t="n">
+        <x:f>IF(ISNUMBER(H22),F22*H22,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K22" s="32" t="n">
+        <x:f>IF(OR(AND(A22&lt;&gt;12,A22&lt;&gt;24),NOT(ISNUMBER(G22)),NOT(ISNUMBER(H22))),1,0)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L22" s="32" t="str">
+        <x:v>O16: reader not selected. Enter 12/24 V system-side rail and input current including any local conversion. Other rail values remain unresolved and outside known subtotal.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" ht="29" customHeight="1">
       <x:c r="A25" s="25" t="str">
         <x:v>Planning parameters</x:v>
@@ -5780,7 +6055,7 @@
       <x:c r="E38" s="19"/>
       <x:c r="F38" s="19"/>
       <x:c r="G38" s="28" t="n">
-        <x:f>SUMIF(A5:A21,24,I5:I21)</x:f>
+        <x:f>SUMIF(A5:A22,24,I5:I22)</x:f>
         <x:v>3.3</x:v>
       </x:c>
       <x:c r="H38" s="19"/>
@@ -5799,7 +6074,7 @@
       <x:c r="E39" s="19"/>
       <x:c r="F39" s="19"/>
       <x:c r="G39" s="28" t="n">
-        <x:f>SUMIF(A5:A21,24,J5:J21)</x:f>
+        <x:f>SUMIF(A5:A22,24,J5:J22)</x:f>
         <x:v>7.1</x:v>
       </x:c>
       <x:c r="H39" s="19"/>
@@ -5818,7 +6093,7 @@
       <x:c r="E40" s="19"/>
       <x:c r="F40" s="19"/>
       <x:c r="G40" s="28" t="n">
-        <x:f>SUMIF(A5:A21,12,I5:I21)</x:f>
+        <x:f>SUMIF(A5:A22,12,I5:I22)</x:f>
         <x:v>2.884</x:v>
       </x:c>
       <x:c r="H40" s="19"/>
@@ -5837,7 +6112,7 @@
       <x:c r="E41" s="19"/>
       <x:c r="F41" s="19"/>
       <x:c r="G41" s="28" t="n">
-        <x:f>SUMIF(A5:A21,12,J5:J21)</x:f>
+        <x:f>SUMIF(A5:A22,12,J5:J22)</x:f>
         <x:v>7.3919999999999995</x:v>
       </x:c>
       <x:c r="H41" s="19"/>
@@ -5856,7 +6131,7 @@
       <x:c r="E42" s="19"/>
       <x:c r="F42" s="19"/>
       <x:c r="G42" s="28" t="n">
-        <x:f>G41*12/(G29*G32)</x:f>
+        <x:f>IF(AND(G29&gt;0,G32&gt;0,G32&lt;=1),G41*12/(G29*G32),"INVALID INPUT")</x:f>
         <x:v>4.1066666666666665</x:v>
       </x:c>
       <x:c r="H42" s="19"/>
@@ -5875,7 +6150,7 @@
       <x:c r="E43" s="19"/>
       <x:c r="F43" s="19"/>
       <x:c r="G43" s="28" t="n">
-        <x:f>G39+G42</x:f>
+        <x:f>IF(ISNUMBER(G42),G39+G42,"INVALID INPUT")</x:f>
         <x:v>11.206666666666667</x:v>
       </x:c>
       <x:c r="H43" s="19"/>
@@ -5894,7 +6169,7 @@
       <x:c r="E44" s="19"/>
       <x:c r="F44" s="19"/>
       <x:c r="G44" s="28" t="n">
-        <x:f>G43*G29</x:f>
+        <x:f>IF(ISNUMBER(G43),G43*G29,"INVALID INPUT")</x:f>
         <x:v>268.96000000000004</x:v>
       </x:c>
       <x:c r="H44" s="19"/>
@@ -5913,8 +6188,8 @@
       <x:c r="E45" s="19"/>
       <x:c r="F45" s="19"/>
       <x:c r="G45" s="19" t="n">
-        <x:f>SUM(K5:K21)</x:f>
-        <x:v>3</x:v>
+        <x:f>SUM(K5:K22)</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H45" s="19"/>
       <x:c r="I45" s="19"/>
@@ -5932,8 +6207,8 @@
       <x:c r="E46" s="19"/>
       <x:c r="F46" s="19"/>
       <x:c r="G46" s="19" t="str">
-        <x:f>IF(G45&gt;0,"HOLD - required load currents missing",IF(G44&gt;G31*G35,"OVER RATED OUTPUT",IF(G44&gt;G31*G35*(1-G34),"ABOVE PLANNING TARGET","Within estimated target; hardware proof pending")))</x:f>
-        <x:v>HOLD - required load currents missing</x:v>
+        <x:f>IF(G56&gt;0,"HOLD - invalid planning inputs",IF(G44&gt;G31*G35,"KNOWN SUBTOTAL EXCEEDS RATED OUTPUT",IF(G44&gt;G31*G35*(1-G34),"KNOWN SUBTOTAL ABOVE PLANNING TARGET",IF(G45&gt;0,"HOLD - load currents and marker supply missing","HOLD - marker supply unresolved; subtotal only"))))</x:f>
+        <x:v>HOLD - load currents and marker supply missing</x:v>
       </x:c>
       <x:c r="H46" s="19"/>
       <x:c r="I46" s="19"/>
@@ -5951,7 +6226,7 @@
       <x:c r="E47" s="19"/>
       <x:c r="F47" s="19"/>
       <x:c r="G47" s="19" t="str">
-        <x:f>IF(ISNUMBER(G33),IF(G41&gt;G33,"EXCEEDS SELECTED BUCK RATING","Within estimated rating; thermal/startup proof pending"),"HOLD - buck not selected")</x:f>
+        <x:f>IF(ISNUMBER(G33),IF(G33&lt;=0,"HOLD - invalid buck rating",IF(G41&gt;G33,"EXCEEDS SELECTED BUCK RATING","Within estimate; thermal/startup proof pending")),"HOLD - buck not selected")</x:f>
         <x:v>HOLD - buck not selected</x:v>
       </x:c>
       <x:c r="H47" s="19"/>
@@ -6007,7 +6282,7 @@
       <x:c r="E50" s="19"/>
       <x:c r="F50" s="19"/>
       <x:c r="G50" s="29" t="n">
-        <x:f>G48/G49</x:f>
+        <x:f>IF(G49&gt;0,G48/G49,"INVALID INPUT")</x:f>
         <x:v>2.81</x:v>
       </x:c>
       <x:c r="H50" s="19"/>
@@ -6045,7 +6320,7 @@
       <x:c r="E53" s="19"/>
       <x:c r="F53" s="19"/>
       <x:c r="G53" s="19" t="str">
-        <x:v>O11: marker power and supply connection unknown; not included in known subtotal.</x:v>
+        <x:v>Marker supply unresolved. NFC reader is flagged in row 22; select rail and current before including its power.</x:v>
       </x:c>
       <x:c r="H53" s="19"/>
       <x:c r="I53" s="19"/>
@@ -6070,6 +6345,25 @@
       <x:c r="J54" s="19"/>
       <x:c r="K54" s="19"/>
       <x:c r="L54" s="19"/>
+    </x:row>
+    <x:row r="56" ht="29" customHeight="1">
+      <x:c r="A56" s="31" t="str">
+        <x:v>Invalid planning-input count</x:v>
+      </x:c>
+      <x:c r="B56" s="31"/>
+      <x:c r="C56" s="31"/>
+      <x:c r="D56" s="31"/>
+      <x:c r="E56" s="31"/>
+      <x:c r="F56" s="31"/>
+      <x:c r="G56" s="31" t="n">
+        <x:f>SUM(IF(OR(D5&lt;0,E5&lt;0,F5&lt;0,E5&gt;D5,F5&gt;D5,G5&lt;0,H5&lt;0),1,0),IF(OR(D6&lt;0,E6&lt;0,F6&lt;0,E6&gt;D6,F6&gt;D6,G6&lt;0,H6&lt;0),1,0),IF(OR(D7&lt;0,E7&lt;0,F7&lt;0,E7&gt;D7,F7&gt;D7,G7&lt;0,H7&lt;0),1,0),IF(OR(D8&lt;0,E8&lt;0,F8&lt;0,E8&gt;D8,F8&gt;D8,G8&lt;0,H8&lt;0),1,0),IF(OR(D9&lt;0,E9&lt;0,F9&lt;0,E9&gt;D9,F9&gt;D9,G9&lt;0,H9&lt;0),1,0),IF(OR(D10&lt;0,E10&lt;0,F10&lt;0,E10&gt;D10,F10&gt;D10,G10&lt;0,H10&lt;0),1,0),IF(OR(D11&lt;0,E11&lt;0,F11&lt;0,E11&gt;D11,F11&gt;D11,G11&lt;0,H11&lt;0),1,0),IF(OR(D12&lt;0,E12&lt;0,F12&lt;0,E12&gt;D12,F12&gt;D12,G12&lt;0,H12&lt;0),1,0),IF(OR(D13&lt;0,E13&lt;0,F13&lt;0,E13&gt;D13,F13&gt;D13,G13&lt;0,H13&lt;0),1,0),IF(OR(D14&lt;0,E14&lt;0,F14&lt;0,E14&gt;D14,F14&gt;D14,G14&lt;0,H14&lt;0),1,0),IF(OR(D15&lt;0,E15&lt;0,F15&lt;0,E15&gt;D15,F15&gt;D15,G15&lt;0,H15&lt;0),1,0),IF(OR(D16&lt;0,E16&lt;0,F16&lt;0,E16&gt;D16,F16&gt;D16,G16&lt;0,H16&lt;0),1,0),IF(OR(D17&lt;0,E17&lt;0,F17&lt;0,E17&gt;D17,F17&gt;D17,G17&lt;0,H17&lt;0),1,0),IF(OR(D18&lt;0,E18&lt;0,F18&lt;0,E18&gt;D18,F18&gt;D18,G18&lt;0,H18&lt;0),1,0),IF(OR(D19&lt;0,E19&lt;0,F19&lt;0,E19&gt;D19,F19&gt;D19,G19&lt;0,H19&lt;0),1,0),IF(OR(D20&lt;0,E20&lt;0,F20&lt;0,E20&gt;D20,F20&gt;D20,G20&lt;0,H20&lt;0),1,0),IF(OR(D21&lt;0,E21&lt;0,F21&lt;0,E21&gt;D21,F21&gt;D21,G21&lt;0,H21&lt;0),1,0),IF(OR(D22&lt;0,E22&lt;0,F22&lt;0,E22&gt;D22,F22&gt;D22,G22&lt;0,H22&lt;0),1,0),IF(OR(G29&lt;=0,G30&lt;=0,G32&lt;=0,G32&gt;1,G34&lt;0,G34&gt;=1,G35&lt;=0,G35&gt;1,G49&lt;=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H56" s="31"/>
+      <x:c r="I56" s="31"/>
+      <x:c r="J56" s="31"/>
+      <x:c r="K56" s="31"/>
+      <x:c r="L56" s="31"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -6127,6 +6421,8 @@
     <x:mergeCell ref="G53:L53"/>
     <x:mergeCell ref="A54:F54"/>
     <x:mergeCell ref="G54:L54"/>
+    <x:mergeCell ref="A56:F56"/>
+    <x:mergeCell ref="G56:L56"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6229,7 +6525,7 @@
         <x:v>Select on-board converter, efficiency, continuous/peak rating, startup and thermal design for every derived load.</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
-        <x:v>SYSCTRL; W07/W04; F12/F14/F18</x:v>
+        <x:v>SYSCTRL onboard SMPS; F12/F14/F18; W03/W05/W25/W35</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="44" customHeight="1">
@@ -6306,10 +6602,10 @@
         <x:v>Electrical / harness</x:v>
       </x:c>
       <x:c r="E10" s="10" t="str">
-        <x:v>Size fuse curves/DC ratings, holders, distribution, wire gauge, voltage drop and connectors. No automatic doubling of pin current by paralleling.</x:v>
+        <x:v>Size SYSCTRL system input, PCB power paths, branch protection and output connectors; establish technology, physical placement and purchase counts. Check gauge, drop, inrush and current sharing.</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
-        <x:v>W03/W04/W06/W07/W24/W25/W26; F1–F18</x:v>
+        <x:v>W03/W05/W24/W25/W26/W29/W30/W34/W35; F1-F18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
@@ -6446,7 +6742,7 @@
         <x:v>Customer / software</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
-        <x:v>Decide DHCP/VLAN/firewall, camera/OCR, lighting zones, NFC/payment, QR/BLE and optional radio hardware.</x:v>
+        <x:v>Decide DHCP/VLAN/firewall, camera/OCR, lighting zones, payment, QR/BLE and optional radio hardware. NFC antenna is selected; reader integration is tracked separately under O16.</x:v>
       </x:c>
       <x:c r="F17" s="9" t="str">
         <x:v>Options remain excluded until approved</x:v>
@@ -6490,6 +6786,26 @@
       </x:c>
       <x:c r="F19" s="9" t="str">
         <x:v>W01–W39; harness manufacturing drawings</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="75" customHeight="1">
+      <x:c r="A20" s="32" t="str">
+        <x:v>O16</x:v>
+      </x:c>
+      <x:c r="B20" s="32" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="C20" s="32" t="str">
+        <x:v>NFC reader and antenna integration</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="str">
+        <x:v>Electrical / mechanical / software</x:v>
+      </x:c>
+      <x:c r="E20" s="32" t="str">
+        <x:v>Antenna selected: Molex 1462362151. Select reader/front end, matching circuit, host interface and supply; verify mounting and actual termination. Budget reader power and any new host harness before release.</x:v>
+      </x:c>
+      <x:c r="F20" s="32" t="str">
+        <x:v>ANT-NFC; NFC-RF; MAINCTRL interface and power budget TBC</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6558,7 +6874,7 @@
         <x:v>brain.md and user decisions through 2026-09-24</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
-        <x:v>Single 24 V PSU; SYSCTRL-derived 12 V; IOCTRL naming; 70 lanes; no UPS/cellular. No junction boxes; sensors connect directly to controller boards.</x:v>
+        <x:v>Latest user correction: power distribution/connector area is part of SYSCTRL. One onboard 24 V-to-12 V SMPS; no separate distribution assembly or junction boxes.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="44" customHeight="1">
@@ -6727,6 +7043,34 @@
       </x:c>
       <x:c r="D17" s="9" t="str">
         <x:v>B3F-4055 candidate tactile switch; mechanical compatibility with bracket remains open.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="65" customHeight="1">
+      <x:c r="A18" s="32" t="str">
+        <x:v>S14</x:v>
+      </x:c>
+      <x:c r="B18" s="32" t="str">
+        <x:v>Molex NFC antenna</x:v>
+      </x:c>
+      <x:c r="C18" s="32" t="str">
+        <x:v>https://www.molex.com/en-us/products/part-detail/1462362151</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="str">
+        <x:v>1462362151: 13.56 MHz, 2.40 uH; 15 x 15 x 0.27 mm, adhesive, 102 mm cable. Manufacturer specifications; integration pending.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="65" customHeight="1">
+      <x:c r="A19" s="32" t="str">
+        <x:v>S15</x:v>
+      </x:c>
+      <x:c r="B19" s="32" t="str">
+        <x:v>User-selected distributor listing</x:v>
+      </x:c>
+      <x:c r="C19" s="32" t="str">
+        <x:v>https://www.digikey.com/en/products/detail/molex/1462362151/15204370</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="str">
+        <x:v>User selected this antenna. Antenna selection does not select the NFC reader or payment functionality.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
